--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14298383980893</v>
+        <v>1.973234873968951</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19149753402969</v>
+        <v>1.981118349279825</v>
       </c>
       <c r="E2" t="n">
-        <v>2.717055604671838</v>
+        <v>0.4415215357591737</v>
       </c>
       <c r="F2" t="n">
-        <v>2.761580327225559</v>
+        <v>0.4487568031741533</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.708872630465253</v>
+        <v>1.090191802450604</v>
       </c>
       <c r="D3" t="n">
-        <v>6.668336879578575</v>
+        <v>1.083604742931519</v>
       </c>
       <c r="E3" t="n">
-        <v>2.717055604671838</v>
+        <v>0.4415215357591737</v>
       </c>
       <c r="F3" t="n">
-        <v>2.761580327225559</v>
+        <v>0.4487568031741533</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
